--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_individual_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_individual_h_3.xlsx
@@ -658,7 +658,7 @@
         <v>0.008409573156748078</v>
       </c>
       <c r="C2" t="n">
-        <v>19039140</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>19039140</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>14524210</v>
+        <v>4652873</v>
       </c>
       <c r="L2" t="n">
-        <v>8953797</v>
+        <v>2725828</v>
       </c>
       <c r="M2" t="n">
-        <v>2404384</v>
+        <v>693387</v>
       </c>
       <c r="N2" t="n">
-        <v>166748</v>
+        <v>36301</v>
       </c>
       <c r="O2" t="n">
-        <v>1383876</v>
+        <v>416688</v>
       </c>
       <c r="P2" t="n">
-        <v>539556</v>
+        <v>167442</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999884963035583</v>
+        <v>0.9999921321868896</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9545006155967712</v>
+        <v>0.913499653339386</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9029477834701538</v>
+        <v>0.823790967464447</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8735920786857605</v>
+        <v>0.7700620889663696</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7595612406730652</v>
+        <v>0.5276461243629456</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9063316583633423</v>
+        <v>0.8224748969078064</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9348205924034119</v>
+        <v>0.8749510049819946</v>
       </c>
       <c r="X2" t="n">
-        <v>19039140</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>19039140</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>14564199</v>
+        <v>4849843</v>
       </c>
       <c r="AG2" t="n">
-        <v>8940980</v>
+        <v>2984316</v>
       </c>
       <c r="AH2" t="n">
-        <v>2402318</v>
+        <v>801097</v>
       </c>
       <c r="AI2" t="n">
-        <v>177308</v>
+        <v>59133</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1377264</v>
+        <v>459291</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567306637763977</v>
+        <v>0.9567072987556458</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9111908674240112</v>
+        <v>0.9112796187400818</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581739068031311</v>
+        <v>0.8579719662666321</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626627445220947</v>
+        <v>0.6624432802200317</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020290970802307</v>
+        <v>0.9019978642463684</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002015533191987188</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>14524210</v>
+        <v>4652873</v>
       </c>
       <c r="E3" t="n">
-        <v>666948</v>
+        <v>403478</v>
       </c>
       <c r="F3" t="n">
-        <v>14393</v>
+        <v>7004</v>
       </c>
       <c r="G3" t="n">
-        <v>1848</v>
+        <v>806</v>
       </c>
       <c r="H3" t="n">
-        <v>382</v>
+        <v>228</v>
       </c>
       <c r="I3" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="J3" t="n">
-        <v>30208641</v>
+        <v>10069570</v>
       </c>
       <c r="K3" t="n">
-        <v>33347830</v>
+        <v>10911004</v>
       </c>
       <c r="L3" t="n">
-        <v>38460703</v>
+        <v>12553834</v>
       </c>
       <c r="M3" t="n">
-        <v>46099158</v>
+        <v>15274892</v>
       </c>
       <c r="N3" t="n">
-        <v>48927428</v>
+        <v>16294169</v>
       </c>
       <c r="O3" t="n">
-        <v>47577417</v>
+        <v>15816662</v>
       </c>
       <c r="P3" t="n">
-        <v>48630534</v>
+        <v>16198768</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9550483822822571</v>
+        <v>0.918739378452301</v>
       </c>
       <c r="S3" t="n">
-        <v>0.911336362361908</v>
+        <v>0.8312704563140869</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8584234714508057</v>
+        <v>0.7423326969146729</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6226866245269775</v>
+        <v>0.4063514471054077</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9059382677078247</v>
+        <v>0.8179992437362671</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9305160045623779</v>
+        <v>0.8662241697311401</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14564199</v>
+        <v>4849843</v>
       </c>
       <c r="Z3" t="n">
-        <v>597304</v>
+        <v>199096</v>
       </c>
       <c r="AA3" t="n">
-        <v>25689</v>
+        <v>8579</v>
       </c>
       <c r="AB3" t="n">
-        <v>20409</v>
+        <v>6817</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30208860</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>33381490</v>
+        <v>11132126</v>
       </c>
       <c r="AG3" t="n">
-        <v>38551659</v>
+        <v>12846342</v>
       </c>
       <c r="AH3" t="n">
-        <v>46050051</v>
+        <v>15349322</v>
       </c>
       <c r="AI3" t="n">
-        <v>48889951</v>
+        <v>16296534</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47570852</v>
+        <v>15856699</v>
       </c>
       <c r="AK3" t="n">
-        <v>48628392</v>
+        <v>16209445</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576779007911682</v>
+        <v>0.9576323628425598</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100318551063538</v>
+        <v>0.9100990891456604</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576858639717102</v>
+        <v>0.8576458692550659</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6621207594871521</v>
+        <v>0.6619316339492798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016098380088806</v>
+        <v>0.901633083820343</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03183927763983192</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>654137</v>
+        <v>417462</v>
       </c>
       <c r="E4" t="n">
-        <v>8953797</v>
+        <v>2725828</v>
       </c>
       <c r="F4" t="n">
-        <v>204903</v>
+        <v>126610</v>
       </c>
       <c r="G4" t="n">
-        <v>4742</v>
+        <v>3111</v>
       </c>
       <c r="H4" t="n">
-        <v>6896</v>
+        <v>5726</v>
       </c>
       <c r="I4" t="n">
-        <v>429</v>
+        <v>370</v>
       </c>
       <c r="J4" t="n">
-        <v>219</v>
+        <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>692344</v>
+        <v>440586</v>
       </c>
       <c r="L4" t="n">
-        <v>962388</v>
+        <v>583055</v>
       </c>
       <c r="M4" t="n">
-        <v>347912</v>
+        <v>207043</v>
       </c>
       <c r="N4" t="n">
-        <v>52784</v>
+        <v>32497</v>
       </c>
       <c r="O4" t="n">
-        <v>143022</v>
+        <v>89939</v>
       </c>
       <c r="P4" t="n">
-        <v>37620</v>
+        <v>23931</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999942183494568</v>
+        <v>0.9999960660934448</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9547744393348694</v>
+        <v>0.9161120057106018</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9071227312088013</v>
+        <v>0.8275138139724731</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8659413456916809</v>
+        <v>0.7559431791305542</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6843470335006714</v>
+        <v>0.4591227471828461</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9061349034309387</v>
+        <v>0.820231020450592</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9326633214950562</v>
+        <v>0.8705657124519348</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>615017</v>
+        <v>204901</v>
       </c>
       <c r="Z4" t="n">
-        <v>8940980</v>
+        <v>2984316</v>
       </c>
       <c r="AA4" t="n">
-        <v>248782</v>
+        <v>83178</v>
       </c>
       <c r="AB4" t="n">
-        <v>16494</v>
+        <v>5500</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>658684</v>
+        <v>219464</v>
       </c>
       <c r="AG4" t="n">
-        <v>871432</v>
+        <v>290547</v>
       </c>
       <c r="AH4" t="n">
-        <v>397019</v>
+        <v>132613</v>
       </c>
       <c r="AI4" t="n">
-        <v>90261</v>
+        <v>30132</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149587</v>
+        <v>49902</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572040438652039</v>
+        <v>0.9571695923805237</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106109738349915</v>
+        <v>0.9106889963150024</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579298257827759</v>
+        <v>0.8578088283538818</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6623916029930115</v>
+        <v>0.6621873378753662</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018194079399109</v>
+        <v>0.9018154144287109</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>22525</v>
+        <v>13751</v>
       </c>
       <c r="E5" t="n">
-        <v>267082</v>
+        <v>159188</v>
       </c>
       <c r="F5" t="n">
-        <v>2404384</v>
+        <v>693387</v>
       </c>
       <c r="G5" t="n">
-        <v>24101</v>
+        <v>14732</v>
       </c>
       <c r="H5" t="n">
-        <v>79829</v>
+        <v>50622</v>
       </c>
       <c r="I5" t="n">
-        <v>3008</v>
+        <v>2385</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>683616</v>
+        <v>411537</v>
       </c>
       <c r="L5" t="n">
-        <v>871112</v>
+        <v>553283</v>
       </c>
       <c r="M5" t="n">
-        <v>396546</v>
+        <v>240678</v>
       </c>
       <c r="N5" t="n">
-        <v>101040</v>
+        <v>53033</v>
       </c>
       <c r="O5" t="n">
-        <v>143685</v>
+        <v>92711</v>
       </c>
       <c r="P5" t="n">
-        <v>40290</v>
+        <v>25859</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999955296516418</v>
+        <v>0.9999969601631165</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9720606207847595</v>
+        <v>0.9480919241905212</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9627700448036194</v>
+        <v>0.9307786226272583</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9848834872245789</v>
+        <v>0.9727265238761902</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9968765377998352</v>
+        <v>0.9947898387908936</v>
       </c>
       <c r="V5" t="n">
-        <v>0.994178295135498</v>
+        <v>0.9888736605644226</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9984180331230164</v>
+        <v>0.9969669580459595</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>24105</v>
+        <v>8036</v>
       </c>
       <c r="Z5" t="n">
-        <v>255382</v>
+        <v>85188</v>
       </c>
       <c r="AA5" t="n">
-        <v>2402318</v>
+        <v>801097</v>
       </c>
       <c r="AB5" t="n">
-        <v>29836</v>
+        <v>9959</v>
       </c>
       <c r="AC5" t="n">
-        <v>87390</v>
+        <v>29152</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>643627</v>
+        <v>214567</v>
       </c>
       <c r="AG5" t="n">
-        <v>883929</v>
+        <v>294795</v>
       </c>
       <c r="AH5" t="n">
-        <v>398612</v>
+        <v>132968</v>
       </c>
       <c r="AI5" t="n">
-        <v>90480</v>
+        <v>30201</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150297</v>
+        <v>50108</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735560417175293</v>
+        <v>0.9735605120658875</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643567204475403</v>
+        <v>0.9643431901931763</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838443994522095</v>
+        <v>0.9838218092918396</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963299632072449</v>
+        <v>0.9963247179985046</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939107298851013</v>
+        <v>0.9939077496528625</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983844757080078</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>15597</v>
+        <v>9327</v>
       </c>
       <c r="E6" t="n">
-        <v>21965</v>
+        <v>14903</v>
       </c>
       <c r="F6" t="n">
-        <v>43705</v>
+        <v>18521</v>
       </c>
       <c r="G6" t="n">
-        <v>166748</v>
+        <v>36301</v>
       </c>
       <c r="H6" t="n">
-        <v>18447</v>
+        <v>9505</v>
       </c>
       <c r="I6" t="n">
-        <v>1308</v>
+        <v>766</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19395</v>
+        <v>6471</v>
       </c>
       <c r="Z6" t="n">
-        <v>16067</v>
+        <v>5370</v>
       </c>
       <c r="AA6" t="n">
-        <v>32633</v>
+        <v>10891</v>
       </c>
       <c r="AB6" t="n">
-        <v>177308</v>
+        <v>59133</v>
       </c>
       <c r="AC6" t="n">
-        <v>20942</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>6050</v>
+        <v>5239</v>
       </c>
       <c r="F7" t="n">
-        <v>83367</v>
+        <v>53705</v>
       </c>
       <c r="G7" t="n">
-        <v>21333</v>
+        <v>13340</v>
       </c>
       <c r="H7" t="n">
-        <v>1383876</v>
+        <v>416688</v>
       </c>
       <c r="I7" t="n">
-        <v>32833</v>
+        <v>20389</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2436</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>88925</v>
+        <v>29635</v>
       </c>
       <c r="AB7" t="n">
-        <v>22727</v>
+        <v>7591</v>
       </c>
       <c r="AC7" t="n">
-        <v>1377264</v>
+        <v>459291</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>343</v>
+        <v>247</v>
       </c>
       <c r="F8" t="n">
-        <v>1544</v>
+        <v>1203</v>
       </c>
       <c r="G8" t="n">
-        <v>760</v>
+        <v>508</v>
       </c>
       <c r="H8" t="n">
-        <v>37468</v>
+        <v>23858</v>
       </c>
       <c r="I8" t="n">
-        <v>539556</v>
+        <v>167442</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
